--- a/mount/node-red/template/template-en.xlsx
+++ b/mount/node-red/template/template-en.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -45,19 +45,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Input must be under 63 characters and can include Chinese, letters, numbers, and underscores.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -69,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0">
+    <comment ref="D1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -87,7 +75,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>int
+          <t>integer
 long
 double
 float
@@ -97,7 +85,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -105,7 +93,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">按照不同协议，填不同值，例如：
+          <t xml:space="preserve">Protocol-Specific Value Formatting Guide​
 </t>
         </r>
         <r>
@@ -123,7 +111,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">：填数组下标 0,1,2,3..
+          <t xml:space="preserve">：Array index [0, 1, 2, 3...]
 .
 </t>
         </r>
@@ -142,7 +130,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">：格式ns=0;s=item1;
+          <t xml:space="preserve">：ns=&lt;NamespaceIndex&gt;;s=&lt;Identifier&gt;;
 </t>
         </r>
         <r>
@@ -160,7 +148,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">：填写地址：bacnet.device1._Statistics._FailedWrites
+          <t xml:space="preserve">：&lt;ProgID&gt;.&lt;Device&gt;.&lt;ItemPath&gt;
 </t>
         </r>
       </text>
@@ -170,7 +158,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <r>
       <rPr>
@@ -180,7 +168,43 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>FolderPath(</t>
+      <t>FilePath(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Required</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>FileAlias</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AttributeName(</t>
     </r>
     <r>
       <rPr>
@@ -213,61 +237,6 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>FileName(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Required</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>FileAlias</t>
-  </si>
-  <si>
-    <r>
-      <t>AttributeName(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Required</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>AttributeType(</t>
     </r>
     <r>
@@ -294,6 +263,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>TagConfiguration(</t>
     </r>
     <r>
@@ -1041,6 +1017,13 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1293,25 +1276,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="28.875" customWidth="1"/>
-    <col min="2" max="2" width="30.25" customWidth="1"/>
-    <col min="3" max="3" width="31.125" customWidth="1"/>
-    <col min="4" max="4" width="33.875" customWidth="1"/>
-    <col min="5" max="5" width="31.75" customWidth="1"/>
-    <col min="6" max="6" width="34.875" customWidth="1"/>
+    <col min="2" max="2" width="31.125" customWidth="1"/>
+    <col min="3" max="3" width="33.875" customWidth="1"/>
+    <col min="4" max="4" width="31.75" customWidth="1"/>
+    <col min="5" max="5" width="34.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:6">
+    <row r="1" ht="28" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1319,9 +1301,6 @@
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/mount/node-red/template/template-en.xlsx
+++ b/mount/node-red/template/template-en.xlsx
@@ -168,7 +168,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>FilePath(</t>
+      <t>Path(</t>
     </r>
     <r>
       <rPr>
@@ -193,7 +193,7 @@
     </r>
   </si>
   <si>
-    <t>FileAlias</t>
+    <t>Alias</t>
   </si>
   <si>
     <r>
@@ -1017,13 +1017,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
